--- a/agriculture 58.xlsx
+++ b/agriculture 58.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
-  <si>
-    <t xml:space="preserve">Annual Growth Rate of  State-wise Yield Statistics of Rubber in India(1950- 2020)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -231,7 +228,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -253,21 +250,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -328,7 +310,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -338,14 +320,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -370,89 +344,82 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H1048576"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.33"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>5</v>
       </c>
+      <c r="B3" s="3" t="n">
+        <v>15.6931900586723</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.80681787822927</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>-16.2236424076641</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>15.6931900586723</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0.80681787822927</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>-16.2236424076641</v>
+      <c r="B4" s="3" t="n">
+        <v>5.94034018063192</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3.93819733389871</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>29.2838631272237</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>5.94034018063192</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>3.93819733389871</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>29.2838631272237</v>
+      <c r="B5" s="3" t="n">
+        <v>1.80185025817557</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>12.2517147301053</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>-11.0717238411271</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>1.80185025817557</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>12.2517147301053</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>-11.0717238411271</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
@@ -513,272 +480,272 @@
       <c r="A18" s="0" t="s">
         <v>20</v>
       </c>
+      <c r="B18" s="3" t="n">
+        <v>5.0682261208577</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-8.63874345549738</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>5.0682261208577</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>-8.63874345549738</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>4.6</v>
+      <c r="B19" s="3" t="n">
+        <v>17.2541743970315</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>9.45558739255014</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-5.35372848948375</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>17.2541743970315</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>9.45558739255014</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>-5.35372848948375</v>
+      <c r="B20" s="3" t="n">
+        <v>-15.9810126582278</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2.09424083769633</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>8.78787878787879</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="5" t="n">
-        <v>-15.9810126582278</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>2.09424083769633</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>8.78787878787879</v>
+      <c r="B21" s="3" t="n">
+        <v>12.9943502824859</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>-1.28205128205128</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>-1.57845868152275</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="5" t="n">
-        <v>12.9943502824859</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>-1.28205128205128</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>-1.57845868152275</v>
+      <c r="B22" s="3" t="n">
+        <v>17.3333333333333</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>7.53246753246753</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>-8.77358490566038</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="5" t="n">
-        <v>17.3333333333333</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>7.53246753246753</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>-8.77358490566038</v>
+      <c r="B23" s="3" t="n">
+        <v>-23.5795454545455</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>4.34782608695652</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-5.17063081695967</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="5" t="n">
-        <v>-23.5795454545455</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>4.34782608695652</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>-5.17063081695967</v>
+      <c r="B24" s="3" t="n">
+        <v>7.24907063197026</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>3.00925925925926</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>8.06979280261723</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="5" t="n">
-        <v>7.24907063197026</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>3.00925925925926</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>8.06979280261723</v>
+      <c r="B25" s="3" t="n">
+        <v>26.3431542461005</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.786516853932584</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>5.3481331987891</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="5" t="n">
-        <v>26.3431542461005</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>0.786516853932584</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>5.3481331987891</v>
+      <c r="B26" s="3" t="n">
+        <v>12.2085048010974</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>3.01003344481605</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>2.58620689655172</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>12.2085048010974</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>3.01003344481605</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>2.58620689655172</v>
+      <c r="B27" s="3" t="n">
+        <v>4.88997555012225</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1.94805194805195</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0.840336134453782</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="5" t="n">
-        <v>4.88997555012225</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>1.94805194805195</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>0.840336134453782</v>
+      <c r="B28" s="3" t="n">
+        <v>15.5011655011655</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2.65392781316348</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>6.75925925925926</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>15.5011655011655</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>2.65392781316348</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>6.75925925925926</v>
+      <c r="B29" s="3" t="n">
+        <v>0.504540867810293</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>5.99793174767322</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>3.03555941023417</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>0.504540867810293</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>5.99793174767322</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>3.03555941023417</v>
+      <c r="B30" s="3" t="n">
+        <v>-3.81526104417671</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>5.36585365853659</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>-3.28282828282828</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="5" t="n">
-        <v>-3.81526104417671</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>5.36585365853659</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>-3.28282828282828</v>
+      <c r="B31" s="3" t="n">
+        <v>2.81837160751566</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>5.46296296296296</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0.174064403829417</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="5" t="n">
-        <v>2.81837160751566</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>5.46296296296296</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>-0.174064403829417</v>
+      <c r="B32" s="3" t="n">
+        <v>2.03045685279188</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>2.19490781387182</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0.959023539668701</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>2.03045685279188</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>2.19490781387182</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0.959023539668701</v>
+      <c r="B33" s="3" t="n">
+        <v>2.08955223880597</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>12.0274914089347</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>4.0587219343696</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>2.08955223880597</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>12.0274914089347</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>4.0587219343696</v>
+      <c r="B34" s="3" t="n">
+        <v>3.02144249512671</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>6.51840490797546</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>-0.4149377593361</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="n">
-        <v>3.02144249512671</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>6.51840490797546</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>-0.4149377593361</v>
+      <c r="B35" s="3" t="n">
+        <v>1.98675496688742</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>3.88768898488121</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>16.3333333333333</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="n">
-        <v>1.98675496688742</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>3.88768898488121</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>16.3333333333333</v>
+      <c r="B36" s="3" t="n">
+        <v>6.02968460111317</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>5.95980595980596</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>4.15472779369628</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="n">
-        <v>6.02968460111317</v>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>5.95980595980596</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>4.15472779369628</v>
-      </c>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
@@ -910,11 +877,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
-        <v>66</v>
-      </c>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/agriculture 58.xlsx
+++ b/agriculture 58.xlsx
@@ -208,13 +208,13 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
+    <t xml:space="preserve">Unit:- </t>
+  </si>
+  <si>
     <t xml:space="preserve">Source: EPWRF (Economic and Political Weekly Research Foundation) 1950-2020</t>
   </si>
   <si>
-    <t xml:space="preserve">Source Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1962-63 to 2013-14: Plantation Crops: Rubber:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    <t xml:space="preserve">Source Description:- 1962-63 to 2013-14: Plantation Crops: Rubber:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
   </si>
   <si>
     <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
@@ -228,7 +228,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -266,6 +266,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -310,7 +316,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -324,6 +330,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -344,7 +358,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1048576"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.88"/>
@@ -857,28 +871,45 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A63:D63"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/agriculture 58.xlsx
+++ b/agriculture 58.xlsx
@@ -208,7 +208,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: EPWRF (Economic and Political Weekly Research Foundation) 1950-2020</t>
@@ -228,7 +228,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -266,12 +266,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -316,7 +310,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -333,11 +327,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -880,28 +870,28 @@
       <c r="D60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/agriculture 58.xlsx
+++ b/agriculture 58.xlsx
@@ -208,7 +208,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: EPWRF (Economic and Political Weekly Research Foundation) 1950-2020</t>
